--- a/output/pdf_financials_xlsx/ICM.xlsx
+++ b/output/pdf_financials_xlsx/ICM.xlsx
@@ -4698,37 +4698,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.075486</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.155199</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.809305</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.735894</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.083201</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.083201</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.084942</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.009225</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.9961</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.560293</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.603943</v>
       </c>
     </row>
     <row r="93">
@@ -8181,7 +8181,11 @@
           <t>Reserves (Note 9) 5,229,210</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9178,7 +9182,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>3.075486</v>
       </c>
@@ -10337,7 +10345,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11435,7 +11447,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -11920,7 +11936,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ICM.xlsx
+++ b/output/pdf_financials_xlsx/ICM.xlsx
@@ -2334,37 +2334,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004733</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.044859</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.321952</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.008801</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.070921</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006238</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.117561</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.23878</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.052541</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.319361</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.036141</v>
       </c>
     </row>
     <row r="35">
@@ -2414,37 +2414,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.009933000000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0012</v>
+        <v>0.046059</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0064</v>
+        <v>0.328352</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0024</v>
+        <v>0.011201</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.072921</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.104947</v>
+        <v>0.111185</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.525919</v>
+        <v>0.6434800000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.291475</v>
+        <v>1.530255</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.084845</v>
+        <v>0.137386</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.319361</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.036141</v>
       </c>
     </row>
     <row r="37">
@@ -2894,37 +2894,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.004733</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.044859</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.473919</v>
+        <v>0.151967</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.008801</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.070921</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.018738</v>
+        <v>0.0125</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.242561</v>
+        <v>0.125</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.379515</v>
+        <v>1.140735</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.867171</v>
+        <v>3.81463</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.611127</v>
+        <v>2.291766</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.4177</v>
+        <v>0.381559</v>
       </c>
     </row>
     <row r="49">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
